--- a/data/output/scored_result.xlsx
+++ b/data/output/scored_result.xlsx
@@ -5,22 +5,35 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Code\Python\llm-eval-framework\data\output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A3B73D23-65FE-4DD9-AE19-B8D7F6A0F2AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42475B72-B2F4-4948-8425-D586FFB4638D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{82BA6C40-3F2A-4FF1-8B2F-5CC772362E25}"/>
   </bookViews>
   <sheets>
     <sheet name="scored_result" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="101">
   <si>
     <t>id</t>
   </si>
@@ -29,12 +42,6 @@
   </si>
   <si>
     <t>expected_output</t>
-  </si>
-  <si>
-    <t>llm_answer</t>
-  </si>
-  <si>
-    <t>分數</t>
   </si>
   <si>
     <t>原因</t>
@@ -253,6 +260,130 @@
   <si>
     <t>平均</t>
     <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>分數</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>llm_answer (medgemma-27b-text-it)</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t>medgemma-27b-it</t>
+    <phoneticPr fontId="18" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">乙醯胺酚 (Yǐ xī àn mǐn fèn) 的英文名稱是 **Acetaminophen**。_x000D_
+</t>
+  </si>
+  <si>
+    <t>正確包含預期的英文名稱 Acetaminophen。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Acetaminophen" 的中文名稱是 **撲熱息痛**。_x000D_
+</t>
+  </si>
+  <si>
+    <t>回答了不同地區常用的譯名『撲熱息痛』，未符合預期的『乙醯胺酚』。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aspirin_x000D_
+</t>
+  </si>
+  <si>
+    <t>回答完全正確。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阿司匹林_x000D_
+</t>
+  </si>
+  <si>
+    <t>『阿司匹林』與『阿斯匹林』字面略有不同，但皆為 Aspirin 的有效譯名。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"阿布帖醇硫酸鹽" 的英文名稱是 **Abametapir sulfate**。_x000D_
+</t>
+  </si>
+  <si>
+    <t>英文名稱回答錯誤（Abametapir sulfate 不是 Albuterol Sulfate）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Albuterol Sulfate 的中文名稱是 **沙丁胺醇硫酸鹽**。_x000D_
+</t>
+  </si>
+  <si>
+    <t>回答了不同常見譯名『沙丁胺醇硫酸鹽』，未符合預期的『阿布帖醇硫酸鹽』。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阿曼他丁鹽酸鹽 (Āmāntādīng yánsuān yán) 的英文名稱是 **Amantadine Hydrochloride**._x000D_
+</t>
+  </si>
+  <si>
+    <t>正確包含預期的英文名稱 Amantadine Hydrochloride。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amantadine Hydrochloride 的中文名稱是：**盐酸金刚烷胺**_x000D_
+</t>
+  </si>
+  <si>
+    <t>回答了『盐酸金刚烷胺』（簡體/別名），未符合預期的『阿曼他丁鹽酸鹽』。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">艾米康絲菌素硫酸鹽 (Amikacin sulfate)_x000D_
+</t>
+  </si>
+  <si>
+    <t>正確包含預期的英文名稱 Amikacin sulfate。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阿米卡星硫酸鹽_x000D_
+</t>
+  </si>
+  <si>
+    <t>回答了『阿米卡星硫酸鹽』，未符合預期的『艾米康絲菌素硫酸鹽』。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diphtheria vaccine_x000D_
+</t>
+  </si>
+  <si>
+    <t>回答正確（僅有大小寫差異）。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">"Diphtheria Vaccine" 的中文名稱是：**白喉疫苗**_x000D_
+</t>
+  </si>
+  <si>
+    <t>正確包含預期的中文名稱『白喉疫苗』。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adsorbed Diphtheria and Tetanus Toxoids and Pertussis Vaccine (Whole Cell)_x000D_
+</t>
+  </si>
+  <si>
+    <t>回答成了包含百日咳的三合一疫苗，錯誤。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">破傷風和白喉吸附疫苗_x000D_
+</t>
+  </si>
+  <si>
+    <t>語意相近，但未完全精確符合預期的標準名稱。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Adult Use Adsorbed Diphtheria-Tetanus Mixed Vaccine_x000D_
+</t>
+  </si>
+  <si>
+    <t>意思相近的翻譯，但與預期的標準英文名稱略有差異。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">破傷風和白喉吸附疫苗（成人用）_x000D_
+</t>
+  </si>
+  <si>
+    <t>語意相近，但詞彙順序與括號使用與預期未完全相符。</t>
   </si>
 </sst>
 </file>
@@ -429,7 +560,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -607,6 +738,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -869,12 +1012,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -883,9 +1023,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -894,10 +1031,22 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1275,369 +1424,532 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85603A46-EA63-4402-85F0-02248879C684}">
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:I18"/>
   <sheetFormatPr defaultRowHeight="17" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" style="5"/>
+    <col min="1" max="1" width="8.7265625" style="3"/>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.7265625" style="5"/>
+    <col min="4" max="4" width="36.7265625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.7265625" style="3"/>
     <col min="6" max="6" width="43" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="41.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="7" customFormat="1" ht="34" x14ac:dyDescent="0.4">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:9" s="5" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="G1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="102" x14ac:dyDescent="0.4">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="D2" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="11">
+        <v>100</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="8">
+        <v>100</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>70</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="119" x14ac:dyDescent="0.4">
-      <c r="A2" s="3">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
+    <row r="3" spans="1:9" ht="68" x14ac:dyDescent="0.4">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="E3" s="11">
+        <v>90</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="H3" s="8">
+        <v>50</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="51" x14ac:dyDescent="0.4">
+      <c r="A4" s="2">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="11">
+        <v>100</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H4" s="8">
+        <v>100</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="51" x14ac:dyDescent="0.4">
+      <c r="A5" s="2">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="11">
+        <v>90</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="8">
+        <v>80</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="85" x14ac:dyDescent="0.4">
+      <c r="A6" s="2">
+        <v>9</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="11">
+        <v>0</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="H6" s="8">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="68" x14ac:dyDescent="0.4">
+      <c r="A7" s="2">
+        <v>10</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="E7" s="11">
+        <v>90</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="8">
+        <v>50</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="119" x14ac:dyDescent="0.4">
+      <c r="A8" s="2">
+        <v>13</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E8" s="11">
+        <v>100</v>
+      </c>
+      <c r="F8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="3">
+      <c r="G8" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="H8" s="8">
         <v>100</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>9</v>
+      <c r="I8" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="102" x14ac:dyDescent="0.4">
-      <c r="A3" s="3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="3">
+    <row r="9" spans="1:9" ht="85" x14ac:dyDescent="0.4">
+      <c r="A9" s="2">
+        <v>14</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="11">
         <v>90</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>13</v>
+      <c r="F9" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="H9" s="8">
+        <v>50</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>84</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="68" x14ac:dyDescent="0.4">
-      <c r="A4" s="3">
-        <v>5</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="3">
+    <row r="10" spans="1:9" ht="68" x14ac:dyDescent="0.4">
+      <c r="A10" s="2">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" s="11">
+        <v>0</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="8">
         <v>100</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>9</v>
+      <c r="I10" s="8" t="s">
+        <v>86</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="51" x14ac:dyDescent="0.4">
-      <c r="A5" s="3">
-        <v>6</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="2" t="s">
+    <row r="11" spans="1:9" ht="51" x14ac:dyDescent="0.4">
+      <c r="A11" s="2">
         <v>18</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="B11" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="11">
         <v>90</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>20</v>
+      <c r="F11" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="H11" s="8">
+        <v>50</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>88</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="85" x14ac:dyDescent="0.4">
-      <c r="A6" s="3">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="12" spans="1:9" ht="102" x14ac:dyDescent="0.4">
+      <c r="A12" s="2">
         <v>21</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="B12" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="11">
+        <v>100</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="8">
+        <v>100</v>
+      </c>
+      <c r="I12" s="8" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="68" x14ac:dyDescent="0.4">
+      <c r="A13" s="2">
         <v>22</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="B13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="11">
+        <v>100</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="H13" s="8">
+        <v>100</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="187" x14ac:dyDescent="0.4">
+      <c r="A14" s="2">
+        <v>25</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="E14" s="11">
+        <v>80</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="H14" s="8">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>24</v>
+      <c r="I14" s="8" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="68" x14ac:dyDescent="0.4">
-      <c r="A7" s="3">
-        <v>10</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="2" t="s">
+    <row r="15" spans="1:9" ht="68" x14ac:dyDescent="0.4">
+      <c r="A15" s="2">
         <v>26</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="E7" s="3">
-        <v>90</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>28</v>
+      <c r="B15" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="E15" s="11">
+        <v>80</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="H15" s="8">
+        <v>80</v>
+      </c>
+      <c r="I15" s="8" t="s">
+        <v>96</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="68" x14ac:dyDescent="0.4">
-      <c r="A8" s="3">
-        <v>13</v>
-      </c>
-      <c r="B8" s="2" t="s">
+    <row r="16" spans="1:9" ht="255" x14ac:dyDescent="0.4">
+      <c r="A16" s="2">
         <v>29</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="B16" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E16" s="11">
+        <v>80</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>97</v>
+      </c>
+      <c r="H16" s="8">
+        <v>80</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="221" x14ac:dyDescent="0.4">
+      <c r="A17" s="2">
         <v>30</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="B17" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="E17" s="11">
+        <v>80</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>99</v>
+      </c>
+      <c r="H17" s="8">
+        <v>80</v>
+      </c>
+      <c r="I17" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>9</v>
-      </c>
     </row>
-    <row r="9" spans="1:6" ht="85" x14ac:dyDescent="0.4">
-      <c r="A9" s="3">
-        <v>14</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E9" s="3">
-        <v>90</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="85" x14ac:dyDescent="0.4">
-      <c r="A10" s="3">
-        <v>17</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E10" s="3">
-        <v>0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="68" x14ac:dyDescent="0.4">
-      <c r="A11" s="3">
-        <v>18</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="3">
-        <v>90</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="136" x14ac:dyDescent="0.4">
-      <c r="A12" s="3">
-        <v>21</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" s="3">
-        <v>100</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="68" x14ac:dyDescent="0.4">
-      <c r="A13" s="3">
-        <v>22</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="3">
-        <v>100</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="306" x14ac:dyDescent="0.4">
-      <c r="A14" s="3">
-        <v>25</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" s="3">
-        <v>80</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="85" x14ac:dyDescent="0.4">
-      <c r="A15" s="3">
-        <v>26</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E15" s="3">
-        <v>80</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" ht="374" x14ac:dyDescent="0.4">
-      <c r="A16" s="3">
-        <v>29</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="3">
-        <v>80</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="340" x14ac:dyDescent="0.4">
-      <c r="A17" s="3">
-        <v>30</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E17" s="3">
-        <v>80</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A18" s="4"/>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="A18" s="2"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="9">
+      <c r="D18" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="4">
         <f>AVERAGE(E2:E17)</f>
         <v>79.375</v>
       </c>
       <c r="F18" s="1"/>
+      <c r="G18" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="H18" s="4">
+        <f>AVERAGE(H2:H17)</f>
+        <v>70</v>
+      </c>
+      <c r="I18" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="18" type="noConversion"/>
